--- a/testVoter.xlsx
+++ b/testVoter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project2\FinalProject\Source Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286650B9-A714-4555-A77F-1F66AD1D8A1B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD14AF97-98C2-4831-B4D3-2E43723E20A7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{2F581578-0329-49A3-B9C3-3DACF9A5F38E}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>email</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>dinhquocdat@gmail.com</t>
+  </si>
+  <si>
+    <t>dqdkma@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -413,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{929A7569-F30E-4CC7-A41D-8BFEF4DAE58E}">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -449,6 +452,11 @@
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -459,6 +467,7 @@
     <hyperlink ref="A5" r:id="rId4" xr:uid="{2D964BC4-D911-4149-8BE9-99B0308613C3}"/>
     <hyperlink ref="A6" r:id="rId5" xr:uid="{F183893A-43DB-4DD4-8869-E5C977F5F0A4}"/>
     <hyperlink ref="A7" r:id="rId6" xr:uid="{A4C970EE-467C-463E-8FC1-F3D99EA5C0BB}"/>
+    <hyperlink ref="A8" r:id="rId7" xr:uid="{8AD10953-830D-4965-A426-11AE033B5BB4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
